--- a/order_forms/028_pizza_order_form--order_forms.xlsx
+++ b/order_forms/028_pizza_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Toppings 2</t>
+          <t>Second Toppings</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Crust</t>
+          <t>Second Crust</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sauces</t>
+          <t>Second Sauce</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hand-tossed</t>
+          <t>thin_crust</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hand-tossed</t>
+          <t>Thin Crust</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>thin_crust</t>
+          <t>thick_crust</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thin Crust</t>
+          <t>Thick Crust</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>first_crust_choices</t>
+          <t>first_sauce_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>thick_crust</t>
+          <t>marinara</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thick Crust</t>
+          <t>Marinara</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>marinara</t>
+          <t>olive_oil</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marinara</t>
+          <t>Olive Oil</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>olive_oil</t>
+          <t>garlic_butter</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Olive Oil</t>
+          <t>Garlic Butter</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>garlic_butter</t>
+          <t>pesto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Garlic Butter</t>
+          <t>Pesto</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>first_sauce_choices</t>
+          <t>first_toppings_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pesto</t>
+          <t>pepperoni</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pesto</t>
+          <t>Pepperoni</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pepperoni</t>
+          <t>sausage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pepperoni</t>
+          <t>Sausage</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sausage</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Mushrooms</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mushrooms</t>
+          <t>olives</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mushrooms</t>
+          <t>Olives</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>first_toppings_choices</t>
+          <t>second_toppings_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>olives</t>
+          <t>pepperoni</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Pepperoni</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pepperoni</t>
+          <t>sausage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pepperoni</t>
+          <t>Sausage</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sausage</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>Mushrooms</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>mushrooms</t>
+          <t>olives</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mushrooms</t>
+          <t>Olives</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>second_toppings_choices</t>
+          <t>second_crust_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>olives</t>
+          <t>hand-tossed</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Hand-tossed</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hand-tossed</t>
+          <t>thin_crust</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hand-tossed</t>
+          <t>Thin Crust</t>
         </is>
       </c>
     </row>
@@ -1675,46 +1675,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>hand-tossed</t>
+          <t>thick_crust</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hand-tossed</t>
+          <t>Thick Crust</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>second_crust_choices</t>
+          <t>second_sauce_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>thin_crust</t>
+          <t>marinara</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thin Crust</t>
+          <t>Marinara</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>second_crust_choices</t>
+          <t>second_sauce_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>thick_crust</t>
+          <t>olive_oil</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thick Crust</t>
+          <t>Olive Oil</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>marinara</t>
+          <t>garlic_butter</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Marinara</t>
+          <t>Garlic Butter</t>
         </is>
       </c>
     </row>
@@ -1743,46 +1743,46 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>olive_oil</t>
+          <t>pesto</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Olive Oil</t>
+          <t>Pesto</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>second_sauce_choices</t>
+          <t>third_toppings_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>garlic_butter</t>
+          <t>pepperoni</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Garlic Butter</t>
+          <t>Pepperoni</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>second_sauce_choices</t>
+          <t>third_toppings_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pesto</t>
+          <t>sausage</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pesto</t>
+          <t>Sausage</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pepperoni</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pepperoni</t>
+          <t>Mushrooms</t>
         </is>
       </c>
     </row>
@@ -1811,44 +1811,10 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sausage</t>
+          <t>olives</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
-        <is>
-          <t>Sausage</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>third_toppings_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>mushrooms</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Mushrooms</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>third_toppings_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>olives</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
         <is>
           <t>Olives</t>
         </is>
